--- a/course-design-2/outputs/tables/ch4/55_stage26_5_province_distribution.xlsx
+++ b/course-design-2/outputs/tables/ch4/55_stage26_5_province_distribution.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_省级岗位数" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_未能映射城市" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_口径与数据来源" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_统计范围与数据来源" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
